--- a/backend/data/reliability_analysis.xlsx
+++ b/backend/data/reliability_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,138 +465,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[독립변수] 셀프리더십</t>
+          <t>[독립변수] 독1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>se1</t>
+          <t>독11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.83</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[독립변수] 셀프리더십</t>
+          <t>[독립변수] 독1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>se2</t>
+          <t>독12</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.853</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[독립변수] 셀프리더십</t>
+          <t>[독립변수] 독1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>se3</t>
+          <t>독13</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.892</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[종속변수] 직무만족</t>
+          <t>[종속변수] 종1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>직무만족</t>
+          <t>종1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.918</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[매개변수] 정서적몰입</t>
+          <t>[매개변수] 매1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>정서적몰입</t>
+          <t>매11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.789</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[매개변수] 자기효능감</t>
+          <t>[매개변수] 매1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>자기효능감</t>
+          <t>매12</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.924</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[조절변수] 성격</t>
+          <t>[매개변수] 매1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>새 1</t>
+          <t>매13</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -606,95 +606,135 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.841</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[조절변수] 성격</t>
+          <t>[매개변수] 매2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>새 2</t>
+          <t>매2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.755</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[조절변수] 성격</t>
+          <t>[조절변수] 조1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>새 3</t>
+          <t>조11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.773</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[조절변수] 성격</t>
+          <t>[조절변수] 조1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>새 4</t>
+          <t>조12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.848</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[조절변수] 성격</t>
+          <t>[조절변수] 조1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>새 5</t>
+          <t>조13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.664</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>[조절변수] 조1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>조14</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>합 계</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>※ 일반적으로 사회과학 연구에서 Cronbach's α 계수가 .60 이상이면 신뢰도에 문제가 없는 것으로 판단함.</t>
         </is>

--- a/backend/data/reliability_analysis.xlsx
+++ b/backend/data/reliability_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.785</v>
+        <v>-0.609</v>
       </c>
     </row>
     <row r="5">
@@ -507,12 +507,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[독립변수] 독1</t>
+          <t>[독립변수] 독2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>독13</t>
+          <t>독22</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -522,49 +522,49 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.887</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[종속변수] 종1</t>
+          <t>[독립변수] 독2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>종1</t>
+          <t>독23</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.902</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[매개변수] 매1</t>
+          <t>[종속변수] 종1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>매11</t>
+          <t>종1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.838</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +585,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.863</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.879</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="11">
@@ -627,7 +627,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.882</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="12">
@@ -648,7 +648,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.898</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="13">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.845</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="14">
@@ -680,61 +680,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>조13</t>
+          <t>조132</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.88</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[조절변수] 조1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>조14</t>
-        </is>
-      </c>
+          <t>합 계</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.781</v>
+        <v>39</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
-        <is>
-          <t>합 계</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>41</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
         <is>
           <t>※ 일반적으로 사회과학 연구에서 Cronbach's α 계수가 .60 이상이면 신뢰도에 문제가 없는 것으로 판단함.</t>
         </is>
